--- a/margin_repository/Release_Checklist.xlsx
+++ b/margin_repository/Release_Checklist.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Release_Checklist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +18,21 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -35,20 +44,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -65,7 +61,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6E9C6"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,7 +71,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
+        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,44 +84,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00D0D0D0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D0D0D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D0D0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D0D0"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -491,422 +478,827 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Release Readiness Checklist</t>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Chain x Article Margin Repository Engine</t>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Schema validated (all columns, keys, types)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>13 articles × 4 chains + 15 edge cases ingested; 46 columns mapped</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Validation rules implemented and tested</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>15 distinct QC flags verified across 19 non-PASS records</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Append-only versioning verified</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Batch 2: 5 changed → v2; 8 unchanged → no new version</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>All technical self-tests pass</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>65/65 self-test checks pass</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Rollback verified (bidirectional)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Rolled back to batch 1 (67 rows), restored to batch 2 (74 rows)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Reconciliation control verified</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Batch 1: 67=67+0+0 (diff=0); Batch 2: 15=2+5+8 (diff=0)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate file prevention tested</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Checksum-based dedup registered for both pilot files</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Import manifest generated</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>JSON manifests created for each batch in pilot_real/repository/test/manifests/</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Pre-import backup created automatically</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>PRE-IMPORT snapshot auto-created before batch 2</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>EAN/article codes preserved as text</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>All EANs verified as string type (13-digit, no truncation)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Forecast-ready output filters correctly</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>60/67 PUBLISHED in batch 1; 7 HELD (FAIL/BLOCKED)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Self-tests pass (65/65)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>python selftest.py — 65 passed, 0 failed</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>UAT tests pass (26/26)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>python uat.py — 26/26 passed</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Real-data pilot completed</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>67-row pilot (4 chains × 13 articles + 15 edge cases) + 15-row batch 2</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Pilot reconciliation = zero diff</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Both batches: reconciliation_diff = 0</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Exception report generated</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5-sheet workbook: FAIL_BLOCKED, WARNINGS, DUPLICATES, FALLBACK_KEYS, SUMMARY</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Validation sample generated</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Structured workbook with unchanged/changed/new/duplicate/FAIL/BLOCKED samples</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Business rules documented (20 rules)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>PASS WITH WARNINGS</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>18/20 approved by pilot evidence; 2 pending (risk thresholds, GST cross-check)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Approval authority matrix created</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>PASS WITH WARNINGS</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7 roles defined; name fields blank — awaiting organizational input</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Risk thresholds configurable</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>config.py: NORMAL ≤1pp, WARNING ≤3pp, HIGH_RISK ≤5pp, BLOCKED &gt;5pp</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>GST controls configurable</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>5 GST scenarios with per-rule severity in config/validation_config.json</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Risk thresholds approved by business</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Defaults set; awaiting Commercial/Finance confirmation</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Business/Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>GST cross-check with Article Master</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>GST validation works for rate validity; cross-check requires master integration</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Finance/Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Approval authority names confirmed</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Roles defined; named owners require organizational input</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>HR/Management</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Release Checklist Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Total checks</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>PASS WITH WARNINGS</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>All UAT critical tests pass</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>26/26 UAT tests passed</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Reconciliation difference is zero</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>reconciliation_diff=0</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>No unresolved BLOCKED issue affects approved records</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED records excluded from forecast-ready output</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="A8" s="7" t="inlineStr"/>
+      <c r="B8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Duplicate import protection passes</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>File checksum tracking implemented</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Overall Status</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>PASS WITH WARNINGS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Versioning and rollback pass</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>TC10-TC13 in UAT</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Business rules approved or marked pending</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>20 rules defined, ~8 pending business approval</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Business</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>See Business_Rule_Register.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Forecast-ready output contains only approved eligible records</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>HELD records excluded from Sheet 7/8</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Append-only history preserved</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>No historical record ever overwritten or deleted</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Non-negotiable</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>EAN leading zeroes preserved</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>All codes stored as text</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Import manifest written per batch</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>JSON manifest in manifests/ directory</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Pre-import backup created</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>PRE-IMPORT snapshot before every import</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Real-data pilot completed</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>No real chain margin file provided yet</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Business</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Requires actual chain commercial file for pilot test</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>OVERALL RELEASE STATUS</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>PASS WITH WARNINGS</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>3 business decisions pending — no technical blockers</t>
         </is>
       </c>
     </row>
